--- a/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>70750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104348</t>
+          <t>104965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227898</t>
+          <t>228690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270125</t>
+          <t>271716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307405</t>
+          <t>309057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>367757</t>
+          <t>367996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389716</t>
+          <t>389099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>423314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196502</t>
+          <t>194911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238729</t>
+          <t>237937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592934</t>
+          <t>592695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>653286</t>
+          <t>651634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283419</t>
+          <t>283556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>341556</t>
+          <t>338691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>517407</t>
+          <t>518488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>553310</t>
+          <t>553619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>814868</t>
+          <t>814023</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>884923</t>
+          <t>881947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>396798</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452070</t>
+          <t>451933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105412</t>
+          <t>104331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473384</t>
+          <t>476360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>543439</t>
+          <t>544284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>236362</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>285571</t>
+          <t>286836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>628368</t>
+          <t>625506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>655135</t>
+          <t>653571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>870900</t>
+          <t>871021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>937893</t>
+          <t>941507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>352215</t>
+          <t>350950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>398944</t>
+          <t>401424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61376</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389637</t>
+          <t>386023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456630</t>
+          <t>456509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148784</t>
+          <t>153718</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196787</t>
+          <t>197461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473760</t>
+          <t>473131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>495838</t>
+          <t>495471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>623681</t>
+          <t>628329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>687789</t>
+          <t>691775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322360</t>
+          <t>321686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370363</t>
+          <t>365429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41882</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347000</t>
+          <t>343014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411108</t>
+          <t>406460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80685</t>
+          <t>81486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114372</t>
+          <t>116356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371857</t>
+          <t>371273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>388822</t>
+          <t>388896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>449087</t>
+          <t>452302</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505876</t>
+          <t>503789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272338</t>
+          <t>270354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306025</t>
+          <t>305224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283805</t>
+          <t>285892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340594</t>
+          <t>337379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100969</t>
+          <t>100145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132720</t>
+          <t>133813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>295866</t>
+          <t>295374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>317189</t>
+          <t>316731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>401170</t>
+          <t>399452</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>445519</t>
+          <t>446463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159863</t>
+          <t>158770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191614</t>
+          <t>192438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189998</t>
+          <t>189054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>234347</t>
+          <t>236065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88602</t>
+          <t>88425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214567</t>
+          <t>216445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251831</t>
+          <t>251653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>285865</t>
+          <t>286101</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330836</t>
+          <t>333948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121281</t>
+          <t>121458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>148582</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82077</t>
+          <t>82255</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119341</t>
+          <t>117463</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212955</t>
+          <t>209843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>257926</t>
+          <t>257690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1063343</t>
+          <t>1064943</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1174164</t>
+          <t>1177799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2789690</t>
+          <t>2791090</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2877311</t>
+          <t>2877241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3881039</t>
+          <t>3878149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4032335</t>
+          <t>4043597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2101497</t>
+          <t>2097862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2212318</t>
+          <t>2210718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>497334</t>
+          <t>497404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>584955</t>
+          <t>583555</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2617972</t>
+          <t>2606710</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2769268</t>
+          <t>2772158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93087</t>
+          <t>93485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133964</t>
+          <t>131884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226657</t>
+          <t>227399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268984</t>
+          <t>268075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>327501</t>
+          <t>330708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385289</t>
+          <t>386711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320182</t>
+          <t>322262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361059</t>
+          <t>360661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161246</t>
+          <t>162155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203573</t>
+          <t>202831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499087</t>
+          <t>497665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556875</t>
+          <t>553668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318596</t>
+          <t>318739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371574</t>
+          <t>371342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520222</t>
+          <t>520681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>553316</t>
+          <t>553052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>850135</t>
+          <t>846079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>914264</t>
+          <t>916768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315513</t>
+          <t>315745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368491</t>
+          <t>368348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>57203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383078</t>
+          <t>380574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447207</t>
+          <t>451263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362104</t>
+          <t>363372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417466</t>
+          <t>415449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653516</t>
+          <t>653391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>679832</t>
+          <t>679576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1020161</t>
+          <t>1024866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1087605</t>
+          <t>1089492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264397</t>
+          <t>266414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319759</t>
+          <t>318491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304106</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371550</t>
+          <t>366845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273583</t>
+          <t>272329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>326277</t>
+          <t>328007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>560206</t>
+          <t>561485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588521</t>
+          <t>587766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>839739</t>
+          <t>841972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>909504</t>
+          <t>910029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288340</t>
+          <t>286610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341034</t>
+          <t>342288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55993</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321312</t>
+          <t>320787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391077</t>
+          <t>388844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144147</t>
+          <t>142469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186063</t>
+          <t>185517</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>389657</t>
+          <t>388773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>416324</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>537902</t>
+          <t>539341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597695</t>
+          <t>596625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242307</t>
+          <t>242853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284223</t>
+          <t>285901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>31143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58143</t>
+          <t>59027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278475</t>
+          <t>279545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338268</t>
+          <t>336829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>94555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130475</t>
+          <t>130059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>294619</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319838</t>
+          <t>320490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393460</t>
+          <t>394746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>446437</t>
+          <t>445963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179311</t>
+          <t>179727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216094</t>
+          <t>215231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58378</t>
+          <t>58411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216346</t>
+          <t>216820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269323</t>
+          <t>268037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>59955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92611</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208360</t>
+          <t>209290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250549</t>
+          <t>247960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279695</t>
+          <t>280658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>331020</t>
+          <t>334460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157240</t>
+          <t>157832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>188712</t>
+          <t>189896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138430</t>
+          <t>141019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180619</t>
+          <t>179689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307810</t>
+          <t>304370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>359135</t>
+          <t>358172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1433624</t>
+          <t>1437310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1559438</t>
+          <t>1559799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2921499</t>
+          <t>2926098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3015622</t>
+          <t>3019903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4384190</t>
+          <t>4386140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4552911</t>
+          <t>4552176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1866281</t>
+          <t>1865920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1992095</t>
+          <t>1988409</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>540686</t>
+          <t>536405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>634809</t>
+          <t>630210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2429116</t>
+          <t>2429851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2597837</t>
+          <t>2595887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103739</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>139720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>232022</t>
+          <t>233245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269139</t>
+          <t>270509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345477</t>
+          <t>345712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403303</t>
+          <t>400278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275562</t>
+          <t>277908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>313889</t>
+          <t>317227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163733</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410080</t>
+          <t>413105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467906</t>
+          <t>467671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328030</t>
+          <t>324957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>372742</t>
+          <t>373769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482379</t>
+          <t>482343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>512401</t>
+          <t>511013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>816940</t>
+          <t>819829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>876589</t>
+          <t>876112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217754</t>
+          <t>216727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262466</t>
+          <t>265539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50208</t>
+          <t>51596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80230</t>
+          <t>80266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276517</t>
+          <t>276994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336166</t>
+          <t>333277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>421213</t>
+          <t>419617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470486</t>
+          <t>470189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>621529</t>
+          <t>622140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>643048</t>
+          <t>643927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1050286</t>
+          <t>1051638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1106287</t>
+          <t>1108359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195909</t>
+          <t>196206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245182</t>
+          <t>246778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220565</t>
+          <t>218493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276566</t>
+          <t>275214</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>355735</t>
+          <t>357405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>408133</t>
+          <t>408545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605804</t>
+          <t>605052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>627435</t>
+          <t>627016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>971607</t>
+          <t>966478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1028577</t>
+          <t>1029930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235198</t>
+          <t>234786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287596</t>
+          <t>285926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262790</t>
+          <t>261437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319760</t>
+          <t>324889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>219980</t>
+          <t>220913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264426</t>
+          <t>266737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>461584</t>
+          <t>462800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481241</t>
+          <t>481178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>688399</t>
+          <t>686730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>747161</t>
+          <t>743026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213492</t>
+          <t>211181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257938</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226503</t>
+          <t>230638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285265</t>
+          <t>286934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137039</t>
+          <t>136425</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172606</t>
+          <t>172399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>336873</t>
+          <t>337657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>358040</t>
+          <t>358121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478814</t>
+          <t>481552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>529463</t>
+          <t>528564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160674</t>
+          <t>160881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196241</t>
+          <t>196855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180624</t>
+          <t>181523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231273</t>
+          <t>228535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84910</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111738</t>
+          <t>111525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244862</t>
+          <t>246712</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289015</t>
+          <t>291810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>339946</t>
+          <t>341061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392030</t>
+          <t>394782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144524</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>171352</t>
+          <t>173142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111154</t>
+          <t>108359</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155307</t>
+          <t>153457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264401</t>
+          <t>261649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>316485</t>
+          <t>315370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1739920</t>
+          <t>1734100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1853938</t>
+          <t>1856067</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3055840</t>
+          <t>3051482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3134887</t>
+          <t>3135285</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4810233</t>
+          <t>4816483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4968766</t>
+          <t>4963963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1531371</t>
+          <t>1529242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1645389</t>
+          <t>1651209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>404693</t>
+          <t>404295</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>483740</t>
+          <t>488098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1956124</t>
+          <t>1960927</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2114657</t>
+          <t>2108407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162232</t>
+          <t>161492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233158</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188349</t>
+          <t>187793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234227</t>
+          <t>234205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>362663</t>
+          <t>367899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451754</t>
+          <t>450402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>166829</t>
+          <t>168622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237755</t>
+          <t>238495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78973</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124851</t>
+          <t>125407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261433</t>
+          <t>262785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>350524</t>
+          <t>345288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>262396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310160</t>
+          <t>310726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>463313</t>
+          <t>463617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>493641</t>
+          <t>492918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>731473</t>
+          <t>729196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>807095</t>
+          <t>806067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113387</t>
+          <t>112821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>164529</t>
+          <t>161151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>48476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128545</t>
+          <t>129573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204167</t>
+          <t>206444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>392716</t>
+          <t>393380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>432150</t>
+          <t>433318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>567782</t>
+          <t>569197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>581482</t>
+          <t>582220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>966901</t>
+          <t>965844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1019170</t>
+          <t>1016498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104188</t>
+          <t>103020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>142958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109170</t>
+          <t>111842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161439</t>
+          <t>162496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215171</t>
+          <t>196737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>660351</t>
+          <t>656396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>686407</t>
+          <t>685192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699811</t>
+          <t>699957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>694878</t>
+          <t>759757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1382222</t>
+          <t>1382062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227435</t>
+          <t>231390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>672615</t>
+          <t>691049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217751</t>
+          <t>217911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>905095</t>
+          <t>840216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>364566</t>
+          <t>367447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>406015</t>
+          <t>408419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>523792</t>
+          <t>524057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>536390</t>
+          <t>536275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>892029</t>
+          <t>892336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>937893</t>
+          <t>938071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155219</t>
+          <t>152815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196668</t>
+          <t>193787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171246</t>
+          <t>171068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217110</t>
+          <t>216803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216102</t>
+          <t>215662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>247397</t>
+          <t>245997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>572771</t>
+          <t>572028</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>599948</t>
+          <t>599535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>767329</t>
+          <t>767722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>897840</t>
+          <t>896448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119669</t>
+          <t>121069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150964</t>
+          <t>151404</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77029</t>
+          <t>78421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>207540</t>
+          <t>207147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126895</t>
+          <t>125844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153194</t>
+          <t>151896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>305815</t>
+          <t>304700</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331037</t>
+          <t>331225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>437752</t>
+          <t>438262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>477353</t>
+          <t>477248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,35%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>130863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155864</t>
+          <t>156915</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94794</t>
+          <t>94606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120016</t>
+          <t>121131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231237</t>
+          <t>231342</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270838</t>
+          <t>270328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1645467</t>
+          <t>1616269</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2299797</t>
+          <t>2302431</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3352739</t>
+          <t>3353826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3457073</t>
+          <t>3455773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4804174</t>
+          <t>4883769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5760368</t>
+          <t>5758566</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1158921</t>
+          <t>1156287</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1813251</t>
+          <t>1842449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>253947</t>
+          <t>255247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>357194</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1409370</t>
+          <t>1411172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2365564</t>
+          <t>2285969</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70750</t>
+          <t>69558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104965</t>
+          <t>103830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228690</t>
+          <t>228998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271716</t>
+          <t>269968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>309057</t>
+          <t>308246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>367996</t>
+          <t>370182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389099</t>
+          <t>390234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423314</t>
+          <t>424506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194911</t>
+          <t>196659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237937</t>
+          <t>237629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592695</t>
+          <t>590509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>651634</t>
+          <t>652445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283556</t>
+          <t>282733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>338691</t>
+          <t>337016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>518488</t>
+          <t>519169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>553619</t>
+          <t>552308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>814023</t>
+          <t>808328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>881947</t>
+          <t>883563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396798</t>
+          <t>398473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451933</t>
+          <t>452756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>70511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104331</t>
+          <t>103650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476360</t>
+          <t>474744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>544284</t>
+          <t>549979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236362</t>
+          <t>235810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>286836</t>
+          <t>286223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625506</t>
+          <t>627447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>653571</t>
+          <t>654922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>871021</t>
+          <t>870432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>941507</t>
+          <t>940778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350950</t>
+          <t>351563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401424</t>
+          <t>401976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>62297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>386023</t>
+          <t>386752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456509</t>
+          <t>457098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153718</t>
+          <t>149740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197461</t>
+          <t>195615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473131</t>
+          <t>472916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>495471</t>
+          <t>495788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>628329</t>
+          <t>625188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>691775</t>
+          <t>692263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>321686</t>
+          <t>323532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365429</t>
+          <t>369407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42511</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343014</t>
+          <t>342526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406460</t>
+          <t>409601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81486</t>
+          <t>82455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116356</t>
+          <t>116316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371273</t>
+          <t>369737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>388896</t>
+          <t>388616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452302</t>
+          <t>451278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503789</t>
+          <t>506384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270354</t>
+          <t>270394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305224</t>
+          <t>304255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285892</t>
+          <t>283297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337379</t>
+          <t>338403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>99619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133813</t>
+          <t>133370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>295374</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316731</t>
+          <t>317564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>399452</t>
+          <t>399841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>446463</t>
+          <t>445682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,13%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158770</t>
+          <t>159213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192438</t>
+          <t>192964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47560</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189054</t>
+          <t>189835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236065</t>
+          <t>235676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88425</t>
+          <t>87654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>216445</t>
+          <t>215661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251653</t>
+          <t>250515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>286101</t>
+          <t>283106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>333948</t>
+          <t>332473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121458</t>
+          <t>122229</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148582</t>
+          <t>149558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82255</t>
+          <t>83393</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117463</t>
+          <t>118247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209843</t>
+          <t>211318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>257690</t>
+          <t>260685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1064943</t>
+          <t>1064692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1177799</t>
+          <t>1178098</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2791090</t>
+          <t>2796494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2877241</t>
+          <t>2881418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3878149</t>
+          <t>3879112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4043597</t>
+          <t>4037308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2097862</t>
+          <t>2097563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2210718</t>
+          <t>2210969</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>497404</t>
+          <t>493227</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>583555</t>
+          <t>578151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2606710</t>
+          <t>2612999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2772158</t>
+          <t>2771195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93485</t>
+          <t>93289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131884</t>
+          <t>130313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227399</t>
+          <t>228447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268075</t>
+          <t>267840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330708</t>
+          <t>328718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>386711</t>
+          <t>387950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322262</t>
+          <t>323833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360661</t>
+          <t>360857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162155</t>
+          <t>162390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202831</t>
+          <t>201783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497665</t>
+          <t>496426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553668</t>
+          <t>555658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318739</t>
+          <t>318274</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371342</t>
+          <t>370402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520681</t>
+          <t>520484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>553052</t>
+          <t>554194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>846079</t>
+          <t>845812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>916768</t>
+          <t>915702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315745</t>
+          <t>316685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368348</t>
+          <t>368813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89574</t>
+          <t>89771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>381640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451263</t>
+          <t>451530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>363372</t>
+          <t>361668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415449</t>
+          <t>415607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653391</t>
+          <t>652665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>679576</t>
+          <t>680013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1024866</t>
+          <t>1027700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1089492</t>
+          <t>1089292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266414</t>
+          <t>266256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318491</t>
+          <t>320195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366845</t>
+          <t>364011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272329</t>
+          <t>272362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>328007</t>
+          <t>325818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>561485</t>
+          <t>558725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>587766</t>
+          <t>586776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>841972</t>
+          <t>835368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>910029</t>
+          <t>909837</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286610</t>
+          <t>288799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342288</t>
+          <t>342255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28433</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54714</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320787</t>
+          <t>320979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388844</t>
+          <t>395448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>142469</t>
+          <t>143156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185517</t>
+          <t>184321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>388773</t>
+          <t>388985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>416657</t>
+          <t>416159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539341</t>
+          <t>538588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>596625</t>
+          <t>596664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242853</t>
+          <t>244049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285901</t>
+          <t>285214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279545</t>
+          <t>279506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336829</t>
+          <t>337582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94555</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130059</t>
+          <t>129192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>294586</t>
+          <t>295948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>320490</t>
+          <t>321231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>394746</t>
+          <t>396633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>445963</t>
+          <t>446845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179727</t>
+          <t>180594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215231</t>
+          <t>215604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216820</t>
+          <t>215938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268037</t>
+          <t>266150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>62087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209290</t>
+          <t>208049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247960</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280658</t>
+          <t>280084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334460</t>
+          <t>333828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157832</t>
+          <t>157495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>189896</t>
+          <t>187764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>141019</t>
+          <t>139826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>179689</t>
+          <t>180930</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>304370</t>
+          <t>305002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>358172</t>
+          <t>358746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1437310</t>
+          <t>1437562</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1559799</t>
+          <t>1557613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2926098</t>
+          <t>2923419</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3019903</t>
+          <t>3017987</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4386140</t>
+          <t>4385240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4552176</t>
+          <t>4552131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1865920</t>
+          <t>1868106</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988409</t>
+          <t>1988157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>538321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>630210</t>
+          <t>632889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2429851</t>
+          <t>2429896</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2595887</t>
+          <t>2596787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100401</t>
+          <t>102560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139720</t>
+          <t>139831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>233245</t>
+          <t>231499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270509</t>
+          <t>269316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345712</t>
+          <t>344874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400278</t>
+          <t>400128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277908</t>
+          <t>277797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>317227</t>
+          <t>315068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125246</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162510</t>
+          <t>164256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413105</t>
+          <t>413255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467671</t>
+          <t>468509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324957</t>
+          <t>327359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>373769</t>
+          <t>374406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482343</t>
+          <t>483150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>511013</t>
+          <t>512083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819829</t>
+          <t>817835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>876112</t>
+          <t>875687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216727</t>
+          <t>216090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265539</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51596</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80266</t>
+          <t>79459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276994</t>
+          <t>277419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333277</t>
+          <t>335271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>419617</t>
+          <t>420994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470189</t>
+          <t>469974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>622140</t>
+          <t>622966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>643927</t>
+          <t>643702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1051638</t>
+          <t>1051202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1108359</t>
+          <t>1107794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196206</t>
+          <t>196421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246778</t>
+          <t>245401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38317</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218493</t>
+          <t>219058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275214</t>
+          <t>275650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>357405</t>
+          <t>358815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>408545</t>
+          <t>409823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605052</t>
+          <t>605922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>627016</t>
+          <t>628071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>966478</t>
+          <t>967721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1029930</t>
+          <t>1028891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234786</t>
+          <t>233508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>285926</t>
+          <t>284516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21020</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261437</t>
+          <t>262476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324889</t>
+          <t>323646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>220913</t>
+          <t>221544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266737</t>
+          <t>267693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>462800</t>
+          <t>460085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481178</t>
+          <t>480968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>686730</t>
+          <t>686148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>743026</t>
+          <t>743517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211181</t>
+          <t>210225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257005</t>
+          <t>256374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230638</t>
+          <t>230147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286934</t>
+          <t>287516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136425</t>
+          <t>135014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>171761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>337657</t>
+          <t>338893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>358121</t>
+          <t>357913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>481552</t>
+          <t>479648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>528564</t>
+          <t>528575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160881</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196855</t>
+          <t>198266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>37915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>181523</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228535</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83120</t>
+          <t>84116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111525</t>
+          <t>112529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246712</t>
+          <t>247344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291810</t>
+          <t>290264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>341061</t>
+          <t>340280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>394782</t>
+          <t>393724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144737</t>
+          <t>143733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173142</t>
+          <t>172146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108359</t>
+          <t>109905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153457</t>
+          <t>152825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261649</t>
+          <t>262707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315370</t>
+          <t>316151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1734100</t>
+          <t>1732899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1856067</t>
+          <t>1853887</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3051482</t>
+          <t>3055023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3135285</t>
+          <t>3134357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4816483</t>
+          <t>4818389</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4963963</t>
+          <t>4971138</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1529242</t>
+          <t>1531422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1651209</t>
+          <t>1652410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>404295</t>
+          <t>405223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>488098</t>
+          <t>484557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1960927</t>
+          <t>1953752</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2108407</t>
+          <t>2106501</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161492</t>
+          <t>164597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231365</t>
+          <t>230305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>211927</t>
+          <t>247501</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>220076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234205</t>
+          <t>270228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>408377</t>
+          <t>446798</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367899</t>
+          <t>406066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>450402</t>
+          <t>493800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203536</t>
+          <t>208497</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168622</t>
+          <t>177488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238495</t>
+          <t>243196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>101273</t>
+          <t>115011</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78995</t>
+          <t>92284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>142436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>304810</t>
+          <t>323507</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262785</t>
+          <t>276505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>345288</t>
+          <t>364239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>285935</t>
+          <t>313266</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262396</t>
+          <t>283993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310726</t>
+          <t>339440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>479432</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>463617</t>
+          <t>447471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>492918</t>
+          <t>477102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>765367</t>
+          <t>778991</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729196</t>
+          <t>743018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>806067</t>
+          <t>807527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>137612</t>
+          <t>163624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>137450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161151</t>
+          <t>192897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32661</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>54262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>170273</t>
+          <t>199632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129573</t>
+          <t>171096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206444</t>
+          <t>235605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>413336</t>
+          <t>468248</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>443059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433318</t>
+          <t>490534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>576164</t>
+          <t>604805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>569197</t>
+          <t>596453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>582220</t>
+          <t>610883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>989500</t>
+          <t>1073052</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>965844</t>
+          <t>1047200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1016498</t>
+          <t>1096373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>123002</t>
+          <t>152589</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103020</t>
+          <t>130303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142958</t>
+          <t>177778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>138840</t>
+          <t>170977</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111842</t>
+          <t>147656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162496</t>
+          <t>196829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>468927</t>
+          <t>507007</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196737</t>
+          <t>481908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>656396</t>
+          <t>531551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>693913</t>
+          <t>716572</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>685192</t>
+          <t>708240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699957</t>
+          <t>722718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1162839</t>
+          <t>1223579</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759757</t>
+          <t>1196863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1382062</t>
+          <t>1248688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>418859</t>
+          <t>193610</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231390</t>
+          <t>169066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>691049</t>
+          <t>218709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>437134</t>
+          <t>213248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217911</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840216</t>
+          <t>239964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>386377</t>
+          <t>418530</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>398525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>408419</t>
+          <t>441204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>531277</t>
+          <t>590445</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>524057</t>
+          <t>582729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>536275</t>
+          <t>596311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>917654</t>
+          <t>1008976</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>892336</t>
+          <t>983837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>938071</t>
+          <t>1031072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174857</t>
+          <t>190816</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152815</t>
+          <t>168142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193787</t>
+          <t>210821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>26126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>191485</t>
+          <t>209226</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171068</t>
+          <t>187130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>234365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>230492</t>
+          <t>253943</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>215662</t>
+          <t>235926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>245997</t>
+          <t>270386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>586226</t>
+          <t>413444</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>572028</t>
+          <t>405232</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>599535</t>
+          <t>420071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>816720</t>
+          <t>667387</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>767722</t>
+          <t>646259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>896448</t>
+          <t>685323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>136574</t>
+          <t>152043</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121069</t>
+          <t>135600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151404</t>
+          <t>170060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>158149</t>
+          <t>177197</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78421</t>
+          <t>159261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>207147</t>
+          <t>198325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>139089</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125844</t>
+          <t>137584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151896</t>
+          <t>166606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>318639</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304700</t>
+          <t>334065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331225</t>
+          <t>362194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>457728</t>
+          <t>499697</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>438262</t>
+          <t>476679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>477248</t>
+          <t>519632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>143670</t>
+          <t>157933</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>130863</t>
+          <t>143592</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156915</t>
+          <t>172614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>107192</t>
+          <t>117177</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94606</t>
+          <t>102415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121131</t>
+          <t>130544</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>250862</t>
+          <t>275110</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231342</t>
+          <t>255175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270328</t>
+          <t>298128</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1338110</t>
+          <t>1219112</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1156287</t>
+          <t>1157319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1842449</t>
+          <t>1280188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>313443</t>
+          <t>349786</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>255247</t>
+          <t>314429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>357194</t>
+          <t>390065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1651553</t>
+          <t>1568897</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1411172</t>
+          <t>1492307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2285969</t>
+          <t>1649132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
